--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3794,7 +3794,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>154</v>
       </c>
@@ -3809,13 +3809,13 @@
         <v>62</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>74</v>
@@ -3897,7 +3897,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>158</v>
       </c>
@@ -3912,13 +3912,13 @@
         <v>159</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>74</v>
@@ -4206,7 +4206,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>172</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
